--- a/MONTHLY TEST.xlsx
+++ b/MONTHLY TEST.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\PycharmProjects\WelcomeScreen\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$B$3:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$A$3:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1 (2)'!$B$3:$G$66</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -795,7 +795,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -861,12 +861,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -913,6 +926,9 @@
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Gridcolumn3" xfId="1"/>
@@ -1257,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <f>SUM(B4:F4)</f>
+        <f t="shared" ref="G4:G35" si="0">SUM(B4:F4)</f>
         <v>0</v>
       </c>
     </row>
@@ -1281,7 +1297,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <f>SUM(B5:F5)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -1305,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <f>SUM(B6:F6)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1329,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <f>SUM(B7:F7)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -1353,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <f>SUM(B8:F8)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -1377,7 +1393,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="2">
-        <f>SUM(B9:F9)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
@@ -1401,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <f>SUM(B10:F10)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
@@ -1425,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2">
-        <f>SUM(B11:F11)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
@@ -1449,7 +1465,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="2">
-        <f>SUM(B12:F12)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
@@ -1473,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2">
-        <f>SUM(B13:F13)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
     </row>
@@ -1497,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <f>SUM(B14:F14)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
@@ -1521,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <f>SUM(B15:F15)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
@@ -1545,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="2">
-        <f>SUM(B16:F16)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
@@ -1569,7 +1585,7 @@
         <v>3</v>
       </c>
       <c r="G17" s="2">
-        <f>SUM(B17:F17)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
@@ -1593,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <f>SUM(B18:F18)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
@@ -1617,7 +1633,7 @@
         <v>3</v>
       </c>
       <c r="G19" s="2">
-        <f>SUM(B19:F19)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
@@ -1641,7 +1657,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <f>SUM(B20:F20)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
@@ -1665,7 +1681,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="2">
-        <f>SUM(B21:F21)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
@@ -1689,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2">
-        <f>SUM(B22:F22)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
@@ -1713,7 +1729,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="2">
-        <f>SUM(B23:F23)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
@@ -1737,7 +1753,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="2">
-        <f>SUM(B24:F24)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
@@ -1761,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="G25" s="2">
-        <f>SUM(B25:F25)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
@@ -1785,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2">
-        <f>SUM(B26:F26)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
@@ -1809,7 +1825,7 @@
         <v>3</v>
       </c>
       <c r="G27" s="2">
-        <f>SUM(B27:F27)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
@@ -1833,7 +1849,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="2">
-        <f>SUM(B28:F28)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
@@ -1857,7 +1873,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <f>SUM(B29:F29)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
@@ -1881,7 +1897,7 @@
         <v>4</v>
       </c>
       <c r="G30" s="2">
-        <f>SUM(B30:F30)</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
@@ -1905,7 +1921,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="2">
-        <f>SUM(B31:F31)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
@@ -1929,7 +1945,7 @@
         <v>3</v>
       </c>
       <c r="G32" s="2">
-        <f>SUM(B32:F32)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
@@ -1953,7 +1969,7 @@
         <v>4</v>
       </c>
       <c r="G33" s="2">
-        <f>SUM(B33:F33)</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
@@ -1977,7 +1993,7 @@
         <v>4</v>
       </c>
       <c r="G34" s="2">
-        <f>SUM(B34:F34)</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
@@ -2001,7 +2017,7 @@
         <v>7</v>
       </c>
       <c r="G35" s="2">
-        <f>SUM(B35:F35)</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
@@ -2025,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="2">
-        <f>SUM(B36:F36)</f>
+        <f t="shared" ref="G36:G67" si="1">SUM(B36:F36)</f>
         <v>39</v>
       </c>
     </row>
@@ -2049,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2">
-        <f>SUM(B37:F37)</f>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
     </row>
@@ -2073,7 +2089,7 @@
         <v>4</v>
       </c>
       <c r="G38" s="2">
-        <f>SUM(B38:F38)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
     </row>
@@ -2097,7 +2113,7 @@
         <v>5</v>
       </c>
       <c r="G39" s="2">
-        <f>SUM(B39:F39)</f>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
     </row>
@@ -2121,7 +2137,7 @@
         <v>3</v>
       </c>
       <c r="G40" s="2">
-        <f>SUM(B40:F40)</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
     </row>
@@ -2145,7 +2161,7 @@
         <v>6</v>
       </c>
       <c r="G41" s="2">
-        <f>SUM(B41:F41)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
     </row>
@@ -2169,7 +2185,7 @@
         <v>5</v>
       </c>
       <c r="G42" s="2">
-        <f>SUM(B42:F42)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
     </row>
@@ -2193,7 +2209,7 @@
         <v>8</v>
       </c>
       <c r="G43" s="2">
-        <f>SUM(B43:F43)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
     </row>
@@ -2217,7 +2233,7 @@
         <v>7</v>
       </c>
       <c r="G44" s="2">
-        <f>SUM(B44:F44)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
     </row>
@@ -2241,7 +2257,7 @@
         <v>7</v>
       </c>
       <c r="G45" s="2">
-        <f>SUM(B45:F45)</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
     </row>
@@ -2265,7 +2281,7 @@
         <v>12</v>
       </c>
       <c r="G46" s="2">
-        <f>SUM(B46:F46)</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
     </row>
@@ -2289,7 +2305,7 @@
         <v>10</v>
       </c>
       <c r="G47" s="2">
-        <f>SUM(B47:F47)</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
     </row>
@@ -2313,7 +2329,7 @@
         <v>6</v>
       </c>
       <c r="G48" s="2">
-        <f>SUM(B48:F48)</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
     </row>
@@ -2337,7 +2353,7 @@
         <v>8</v>
       </c>
       <c r="G49" s="2">
-        <f>SUM(B49:F49)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
     </row>
@@ -2361,7 +2377,7 @@
         <v>11</v>
       </c>
       <c r="G50" s="2">
-        <f>SUM(B50:F50)</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
     </row>
@@ -2385,7 +2401,7 @@
         <v>4</v>
       </c>
       <c r="G51" s="2">
-        <f>SUM(B51:F51)</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
     </row>
@@ -2409,7 +2425,7 @@
         <v>13</v>
       </c>
       <c r="G52" s="2">
-        <f>SUM(B52:F52)</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
     </row>
@@ -2433,7 +2449,7 @@
         <v>12</v>
       </c>
       <c r="G53" s="2">
-        <f>SUM(B53:F53)</f>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
     </row>
@@ -2457,7 +2473,7 @@
         <v>12</v>
       </c>
       <c r="G54" s="2">
-        <f>SUM(B54:F54)</f>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
     </row>
@@ -2481,7 +2497,7 @@
         <v>6</v>
       </c>
       <c r="G55" s="2">
-        <f>SUM(B55:F55)</f>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
     </row>
@@ -2505,7 +2521,7 @@
         <v>7</v>
       </c>
       <c r="G56" s="2">
-        <f>SUM(B56:F56)</f>
+        <f t="shared" si="1"/>
         <v>61</v>
       </c>
     </row>
@@ -2529,7 +2545,7 @@
         <v>7</v>
       </c>
       <c r="G57" s="2">
-        <f>SUM(B57:F57)</f>
+        <f t="shared" si="1"/>
         <v>61</v>
       </c>
     </row>
@@ -2553,7 +2569,7 @@
         <v>14</v>
       </c>
       <c r="G58" s="2">
-        <f>SUM(B58:F58)</f>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
     </row>
@@ -2577,7 +2593,7 @@
         <v>11</v>
       </c>
       <c r="G59" s="2">
-        <f>SUM(B59:F59)</f>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
     </row>
@@ -2601,7 +2617,7 @@
         <v>11</v>
       </c>
       <c r="G60" s="2">
-        <f>SUM(B60:F60)</f>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
     </row>
@@ -2625,7 +2641,7 @@
         <v>9</v>
       </c>
       <c r="G61" s="2">
-        <f>SUM(B61:F61)</f>
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
     </row>
@@ -2649,7 +2665,7 @@
         <v>15</v>
       </c>
       <c r="G62" s="2">
-        <f>SUM(B62:F62)</f>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
     </row>
@@ -2673,7 +2689,7 @@
         <v>14</v>
       </c>
       <c r="G63" s="2">
-        <f>SUM(B63:F63)</f>
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
     </row>
@@ -2697,7 +2713,7 @@
         <v>12</v>
       </c>
       <c r="G64" s="2">
-        <f>SUM(B64:F64)</f>
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
     </row>
@@ -2721,7 +2737,7 @@
         <v>13</v>
       </c>
       <c r="G65" s="2">
-        <f>SUM(B65:F65)</f>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
     </row>
@@ -2745,7 +2761,7 @@
         <v>15</v>
       </c>
       <c r="G66" s="2">
-        <f>SUM(B66:F66)</f>
+        <f t="shared" si="1"/>
         <v>87</v>
       </c>
     </row>
@@ -3699,8 +3715,8 @@
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
     </row>
-    <row r="3" spans="1:13" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    <row r="3" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>232</v>
       </c>
       <c r="B3" s="2"/>
@@ -3724,39 +3740,39 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="15">
+      <c r="A4" s="20">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="C4" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <f t="shared" ref="H4:H35" si="0">SUM(C4:G4)</f>
-        <v>0</v>
+        <f>SUM(C4:G4)</f>
+        <v>19</v>
       </c>
       <c r="L4" s="13"/>
     </row>
     <row r="5" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="15">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -3765,810 +3781,810 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(C5:G5)</f>
+        <v>0</v>
       </c>
       <c r="L5" s="14"/>
       <c r="M5" s="14"/>
     </row>
     <row r="6" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="15">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>SUM(C6:G6)</f>
+        <v>39</v>
       </c>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
     </row>
     <row r="7" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="15">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2">
         <v>2</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>SUM(C7:G7)</f>
+        <v>42</v>
       </c>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
     </row>
     <row r="8" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="15">
-        <v>54</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C8" s="2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>SUM(C8:G8)</f>
+        <v>18</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
     </row>
     <row r="9" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2">
         <v>5</v>
       </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
       <c r="E9" s="2">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2">
         <v>1</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
       </c>
       <c r="G9" s="2">
         <v>6</v>
       </c>
       <c r="H9" s="2">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>SUM(C9:G9)</f>
+        <v>44</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
     </row>
     <row r="10" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2">
+        <v>12</v>
+      </c>
+      <c r="E10" s="2">
+        <v>18</v>
+      </c>
+      <c r="F10" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" s="2">
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="2">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
       <c r="H10" s="2">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f>SUM(C10:G10)</f>
+        <v>76</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
     </row>
     <row r="11" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="15">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F11" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <v>7</v>
+      </c>
+      <c r="H11" s="17">
+        <f>SUM(C11:G11)</f>
+        <v>61</v>
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
     </row>
     <row r="12" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C12" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G12" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>SUM(C12:G12)</f>
+        <v>87</v>
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
     </row>
     <row r="13" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="15">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G13" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13" s="2">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>SUM(C13:G13)</f>
+        <v>44</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
     </row>
     <row r="14" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="15">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2">
+        <v>11</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2">
+        <v>3</v>
+      </c>
+      <c r="H14" s="2">
+        <f>SUM(C14:G14)</f>
         <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="2">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2">
-        <v>5</v>
-      </c>
-      <c r="E14" s="2">
-        <v>7</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2">
-        <f t="shared" si="0"/>
-        <v>21</v>
       </c>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
     </row>
     <row r="15" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="15">
-        <v>32</v>
+      <c r="A15" s="18">
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C15" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F15" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <f>SUM(C15:G15)</f>
+        <v>30</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
     </row>
     <row r="16" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="15">
-        <v>36</v>
+      <c r="A16" s="18">
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C16" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D16" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G16" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H16" s="2">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <f>SUM(C16:G16)</f>
+        <v>57</v>
       </c>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
     </row>
     <row r="17" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <f>SUM(C17:G17)</f>
+        <v>15</v>
       </c>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
     </row>
     <row r="18" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="15">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C18" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2">
         <v>11</v>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
       <c r="E18" s="2">
+        <v>16</v>
+      </c>
+      <c r="F18" s="2">
         <v>6</v>
       </c>
-      <c r="F18" s="2">
-        <v>8</v>
-      </c>
       <c r="G18" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H18" s="2">
-        <f t="shared" si="0"/>
-        <v>26</v>
+        <f>SUM(C18:G18)</f>
+        <v>58</v>
       </c>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
     </row>
     <row r="19" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="15">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C19" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" s="2">
         <v>4</v>
       </c>
       <c r="E19" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F19" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H19" s="2">
-        <f t="shared" si="0"/>
-        <v>26</v>
+        <f>SUM(C19:G19)</f>
+        <v>45</v>
       </c>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
     </row>
     <row r="20" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="15">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F20" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" s="2">
-        <f t="shared" si="0"/>
-        <v>26</v>
+        <f>SUM(C20:G20)</f>
+        <v>36</v>
       </c>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
     </row>
     <row r="21" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="15">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C21" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D21" s="2">
         <v>6</v>
       </c>
       <c r="E21" s="2">
+        <v>13</v>
+      </c>
+      <c r="F21" s="2">
         <v>5</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
       </c>
       <c r="G21" s="2">
         <v>2</v>
       </c>
       <c r="H21" s="2">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <f>SUM(C21:G21)</f>
+        <v>37</v>
       </c>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
     </row>
     <row r="22" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="18">
-        <v>12</v>
+      <c r="A22" s="15">
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C22" s="2">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2">
         <v>9</v>
       </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
       <c r="E22" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G22" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2">
-        <f t="shared" si="0"/>
-        <v>30</v>
+        <f>SUM(C22:G22)</f>
+        <v>43</v>
       </c>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
     </row>
     <row r="23" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="15">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C23" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F23" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
       </c>
       <c r="H23" s="2">
-        <f t="shared" si="0"/>
-        <v>30</v>
+        <f>SUM(C23:G23)</f>
+        <v>34</v>
       </c>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
     </row>
     <row r="24" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="15">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C24" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D24" s="2">
+        <v>5</v>
+      </c>
+      <c r="E24" s="2">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2">
         <v>4</v>
       </c>
-      <c r="E24" s="2">
-        <v>16</v>
-      </c>
-      <c r="F24" s="2">
-        <v>2</v>
-      </c>
       <c r="G24" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <f>SUM(C24:G24)</f>
+        <v>38</v>
       </c>
       <c r="L24" s="16"/>
       <c r="M24" s="15"/>
     </row>
     <row r="25" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="15">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="C25" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D25" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G25" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H25" s="2">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <f>SUM(C25:G25)</f>
+        <v>70</v>
       </c>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
     </row>
     <row r="26" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="15">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C26" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <f>SUM(C26:G26)</f>
         <v>3</v>
-      </c>
-      <c r="E26" s="2">
-        <v>11</v>
-      </c>
-      <c r="F26" s="2">
-        <v>5</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <f t="shared" si="0"/>
-        <v>33</v>
       </c>
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
     </row>
     <row r="27" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="15">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C27" s="2">
         <v>16</v>
       </c>
       <c r="D27" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E27" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F27" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G27" s="2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H27" s="2">
-        <f t="shared" si="0"/>
-        <v>33</v>
+        <f>SUM(C27:G27)</f>
+        <v>78</v>
       </c>
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
     </row>
     <row r="28" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C28" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F28" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="2">
-        <f t="shared" si="0"/>
-        <v>34</v>
+        <f>SUM(C28:G28)</f>
+        <v>21</v>
       </c>
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
     </row>
     <row r="29" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="15">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C29" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E29" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F29" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G29" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H29" s="2">
-        <f t="shared" si="0"/>
-        <v>34</v>
+        <f>SUM(C29:G29)</f>
+        <v>61</v>
       </c>
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
     </row>
     <row r="30" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="15">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C30" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D30" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G30" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H30" s="2">
-        <f t="shared" si="0"/>
-        <v>36</v>
+        <f>SUM(C30:G30)</f>
+        <v>49</v>
       </c>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
     </row>
     <row r="31" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="15">
+        <v>28</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="2">
+        <v>14</v>
+      </c>
+      <c r="D31" s="2">
+        <v>9</v>
+      </c>
+      <c r="E31" s="2">
         <v>18</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="2">
-        <v>11</v>
-      </c>
-      <c r="D31" s="2">
-        <v>6</v>
-      </c>
-      <c r="E31" s="2">
-        <v>13</v>
-      </c>
       <c r="F31" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G31" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H31" s="2">
-        <f t="shared" si="0"/>
-        <v>37</v>
+        <f>SUM(C31:G31)</f>
+        <v>64</v>
       </c>
       <c r="L31" s="15"/>
       <c r="M31" s="15"/>
     </row>
     <row r="32" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="15">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C32" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D32" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G32" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H32" s="2">
-        <f t="shared" si="0"/>
-        <v>37</v>
+        <f>SUM(C32:G32)</f>
+        <v>33</v>
       </c>
       <c r="L32" s="15"/>
       <c r="M32" s="15"/>
     </row>
     <row r="33" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="15">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C33" s="2">
         <v>13</v>
@@ -4580,971 +4596,971 @@
         <v>12</v>
       </c>
       <c r="F33" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G33" s="2">
         <v>4</v>
       </c>
       <c r="H33" s="2">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f>SUM(C33:G33)</f>
+        <v>40</v>
       </c>
       <c r="L33" s="15"/>
       <c r="M33" s="15"/>
     </row>
     <row r="34" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="15">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="C34" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2">
+        <f>SUM(C34:G34)</f>
         <v>6</v>
-      </c>
-      <c r="E34" s="2">
-        <v>6</v>
-      </c>
-      <c r="F34" s="2">
-        <v>4</v>
-      </c>
-      <c r="G34" s="2">
-        <v>4</v>
-      </c>
-      <c r="H34" s="2">
-        <f t="shared" si="0"/>
-        <v>38</v>
       </c>
       <c r="L34" s="15"/>
       <c r="M34" s="15"/>
     </row>
     <row r="35" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="15">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C35" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2">
         <v>6</v>
-      </c>
-      <c r="E35" s="2">
-        <v>9</v>
       </c>
       <c r="F35" s="2">
         <v>2</v>
       </c>
       <c r="G35" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H35" s="2">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f>SUM(C35:G35)</f>
+        <v>24</v>
       </c>
       <c r="L35" s="15"/>
       <c r="M35" s="15"/>
     </row>
     <row r="36" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="15">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C36" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D36" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2">
+        <v>16</v>
+      </c>
+      <c r="G36" s="2">
         <v>6</v>
       </c>
-      <c r="G36" s="2">
-        <v>2</v>
-      </c>
       <c r="H36" s="2">
-        <f t="shared" ref="H36:H66" si="1">SUM(C36:G36)</f>
-        <v>39</v>
+        <f>SUM(C36:G36)</f>
+        <v>59</v>
       </c>
       <c r="L36" s="15"/>
       <c r="M36" s="15"/>
     </row>
     <row r="37" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="15">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C37" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F37" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G37" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2">
-        <f t="shared" si="1"/>
-        <v>39</v>
+        <f>SUM(C37:G37)</f>
+        <v>33</v>
       </c>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
     </row>
     <row r="38" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C38" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E38" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F38" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38" s="2">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f>SUM(C38:G38)</f>
+        <v>24</v>
       </c>
       <c r="L38" s="15"/>
       <c r="M38" s="15"/>
     </row>
     <row r="39" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A39" s="15">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="2">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2">
         <v>4</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2">
-        <v>14</v>
-      </c>
-      <c r="D39" s="2">
-        <v>8</v>
-      </c>
       <c r="E39" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F39" s="2">
         <v>2</v>
       </c>
       <c r="G39" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H39" s="2">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f>SUM(C39:G39)</f>
+        <v>32</v>
       </c>
       <c r="L39" s="15"/>
       <c r="M39" s="15"/>
     </row>
     <row r="40" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A40" s="15">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C40" s="2">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2">
         <v>14</v>
       </c>
-      <c r="D40" s="2">
-        <v>9</v>
-      </c>
       <c r="E40" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F40" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G40" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H40" s="2">
-        <f t="shared" si="1"/>
-        <v>43</v>
+        <f>SUM(C40:G40)</f>
+        <v>76</v>
       </c>
       <c r="L40" s="15"/>
       <c r="M40" s="15"/>
     </row>
     <row r="41" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A41" s="15">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="2">
+        <v>11</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
         <v>6</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2">
-        <v>17</v>
-      </c>
-      <c r="D41" s="2">
-        <v>5</v>
-      </c>
-      <c r="E41" s="2">
-        <v>15</v>
-      </c>
       <c r="F41" s="2">
+        <v>8</v>
+      </c>
+      <c r="G41" s="2">
         <v>1</v>
       </c>
-      <c r="G41" s="2">
-        <v>6</v>
-      </c>
       <c r="H41" s="2">
-        <f t="shared" si="1"/>
-        <v>44</v>
+        <f>SUM(C41:G41)</f>
+        <v>26</v>
       </c>
       <c r="L41" s="15"/>
       <c r="M41" s="15"/>
     </row>
     <row r="42" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="15">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="2">
+        <v>18</v>
+      </c>
+      <c r="D42" s="2">
         <v>10</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="E42" s="2">
+        <v>19</v>
+      </c>
+      <c r="F42" s="2">
         <v>11</v>
       </c>
-      <c r="C42" s="2">
-        <v>14</v>
-      </c>
-      <c r="D42" s="2">
-        <v>5</v>
-      </c>
-      <c r="E42" s="2">
-        <v>15</v>
-      </c>
-      <c r="F42" s="2">
-        <v>5</v>
-      </c>
       <c r="G42" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H42" s="2">
-        <f t="shared" si="1"/>
-        <v>44</v>
+        <f>SUM(C42:G42)</f>
+        <v>67</v>
       </c>
       <c r="L42" s="15"/>
       <c r="M42" s="15"/>
     </row>
     <row r="43" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A43" s="15">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C43" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D43" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2">
         <v>17</v>
       </c>
       <c r="F43" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G43" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H43" s="2">
-        <f t="shared" si="1"/>
-        <v>45</v>
+        <f>SUM(C43:G43)</f>
+        <v>47</v>
       </c>
       <c r="L43" s="15"/>
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A44" s="15">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C44" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44" s="2">
+        <v>9</v>
+      </c>
+      <c r="E44" s="2">
+        <v>3</v>
+      </c>
+      <c r="F44" s="2">
         <v>7</v>
       </c>
-      <c r="E44" s="2">
-        <v>16</v>
-      </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
       <c r="G44" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H44" s="2">
-        <f t="shared" si="1"/>
-        <v>46</v>
+        <f>SUM(C44:G44)</f>
+        <v>37</v>
       </c>
       <c r="L44" s="15"/>
       <c r="M44" s="15"/>
     </row>
     <row r="45" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A45" s="15">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C45" s="2">
+        <v>19</v>
+      </c>
+      <c r="D45" s="2">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2">
         <v>13</v>
-      </c>
-      <c r="D45" s="2">
-        <v>2</v>
-      </c>
-      <c r="E45" s="2">
-        <v>17</v>
       </c>
       <c r="F45" s="2">
         <v>8</v>
       </c>
       <c r="G45" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H45" s="2">
-        <f t="shared" si="1"/>
-        <v>47</v>
+        <f>SUM(C45:G45)</f>
+        <v>52</v>
       </c>
       <c r="L45" s="15"/>
       <c r="M45" s="15"/>
     </row>
     <row r="46" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A46" s="15">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C46" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F46" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G46" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H46" s="2">
-        <f t="shared" si="1"/>
-        <v>47</v>
+        <f>SUM(C46:G46)</f>
+        <v>26</v>
       </c>
       <c r="L46" s="15"/>
       <c r="M46" s="15"/>
     </row>
     <row r="47" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A47" s="15">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C47" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D47" s="2">
         <v>5</v>
       </c>
       <c r="E47" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F47" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G47" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H47" s="2">
-        <f t="shared" si="1"/>
-        <v>47</v>
+        <f>SUM(C47:G47)</f>
+        <v>26</v>
       </c>
       <c r="L47" s="15"/>
       <c r="M47" s="15"/>
     </row>
     <row r="48" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A48" s="15">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C48" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D48" s="2">
+        <v>6</v>
+      </c>
+      <c r="E48" s="2">
+        <v>10</v>
+      </c>
+      <c r="F48" s="2">
+        <v>9</v>
+      </c>
+      <c r="G48" s="2">
         <v>11</v>
       </c>
-      <c r="E48" s="2">
-        <v>9</v>
-      </c>
-      <c r="F48" s="2">
-        <v>4</v>
-      </c>
-      <c r="G48" s="2">
-        <v>6</v>
-      </c>
       <c r="H48" s="2">
-        <f t="shared" si="1"/>
-        <v>48</v>
+        <f>SUM(C48:G48)</f>
+        <v>51</v>
       </c>
       <c r="L48" s="15"/>
       <c r="M48" s="15"/>
     </row>
     <row r="49" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A49" s="15">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C49" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D49" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E49" s="2">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2">
+        <v>6</v>
+      </c>
+      <c r="H49" s="2">
+        <f>SUM(C49:G49)</f>
         <v>12</v>
-      </c>
-      <c r="F49" s="2">
-        <v>8</v>
-      </c>
-      <c r="G49" s="2">
-        <v>8</v>
-      </c>
-      <c r="H49" s="2">
-        <f t="shared" si="1"/>
-        <v>49</v>
       </c>
       <c r="L49" s="15"/>
       <c r="M49" s="15"/>
     </row>
     <row r="50" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A50" s="15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C50" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D50" s="2">
         <v>6</v>
       </c>
       <c r="E50" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F50" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G50" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H50" s="2">
-        <f t="shared" si="1"/>
-        <v>51</v>
+        <f>SUM(C50:G50)</f>
+        <v>28</v>
       </c>
       <c r="L50" s="15"/>
       <c r="M50" s="15"/>
     </row>
     <row r="51" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A51" s="15">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C51" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D51" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E51" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F51" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G51" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H51" s="2">
-        <f t="shared" si="1"/>
-        <v>52</v>
+        <f>SUM(C51:G51)</f>
+        <v>34</v>
       </c>
       <c r="L51" s="15"/>
       <c r="M51" s="15"/>
     </row>
     <row r="52" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A52" s="15">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C52" s="2">
         <v>12</v>
       </c>
       <c r="D52" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E52" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F52" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G52" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H52" s="2">
-        <f t="shared" si="1"/>
-        <v>52</v>
+        <f>SUM(C52:G52)</f>
+        <v>30</v>
       </c>
       <c r="L52" s="15"/>
       <c r="M52" s="15"/>
     </row>
     <row r="53" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="18">
-        <v>13</v>
+      <c r="A53" s="15">
+        <v>50</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C53" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D53" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F53" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G53" s="2">
         <v>12</v>
       </c>
       <c r="H53" s="2">
-        <f t="shared" si="1"/>
-        <v>57</v>
+        <f>SUM(C53:G53)</f>
+        <v>47</v>
       </c>
       <c r="L53" s="15"/>
       <c r="M53" s="15"/>
     </row>
     <row r="54" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A54" s="15">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="C54" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D54" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E54" s="2">
         <v>16</v>
       </c>
       <c r="F54" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H54" s="2">
-        <f t="shared" si="1"/>
-        <v>58</v>
+        <f>SUM(C54:G54)</f>
+        <v>46</v>
       </c>
       <c r="L54" s="15"/>
       <c r="M54" s="15"/>
     </row>
     <row r="55" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A55" s="15">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C55" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D55" s="2">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2">
+        <v>2</v>
+      </c>
+      <c r="G55" s="2">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2">
+        <f>SUM(C55:G55)</f>
         <v>8</v>
-      </c>
-      <c r="E55" s="2">
-        <v>14</v>
-      </c>
-      <c r="F55" s="2">
-        <v>16</v>
-      </c>
-      <c r="G55" s="2">
-        <v>6</v>
-      </c>
-      <c r="H55" s="2">
-        <f t="shared" si="1"/>
-        <v>59</v>
       </c>
       <c r="L55" s="16"/>
       <c r="M55" s="15"/>
     </row>
     <row r="56" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A56" s="15">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C56" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D56" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E56" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F56" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G56" s="2">
-        <v>7</v>
-      </c>
-      <c r="H56" s="17">
-        <f t="shared" si="1"/>
-        <v>61</v>
+        <v>0</v>
+      </c>
+      <c r="H56" s="2">
+        <f>SUM(C56:G56)</f>
+        <v>39</v>
       </c>
       <c r="L56" s="15"/>
       <c r="M56" s="15"/>
     </row>
     <row r="57" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A57" s="15">
-        <v>26</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="C57" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D57" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E57" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F57" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2">
-        <f t="shared" si="1"/>
-        <v>61</v>
+        <f>SUM(C57:G57)</f>
+        <v>8</v>
       </c>
       <c r="L57" s="15"/>
       <c r="M57" s="15"/>
     </row>
     <row r="58" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A58" s="15">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C58" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D58" s="2">
         <v>9</v>
       </c>
       <c r="E58" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F58" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G58" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H58" s="2">
-        <f t="shared" si="1"/>
-        <v>64</v>
+        <f>SUM(C58:G58)</f>
+        <v>52</v>
       </c>
       <c r="L58" s="15"/>
       <c r="M58" s="15"/>
     </row>
     <row r="59" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A59" s="15">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C59" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D59" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E59" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F59" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G59" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H59" s="2">
-        <f t="shared" si="1"/>
-        <v>65</v>
+        <f>SUM(C59:G59)</f>
+        <v>38</v>
       </c>
       <c r="L59" s="15"/>
       <c r="M59" s="15"/>
     </row>
     <row r="60" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A60" s="15">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C60" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D60" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E60" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F60" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G60" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H60" s="2">
-        <f t="shared" si="1"/>
-        <v>66</v>
+        <f>SUM(C60:G60)</f>
+        <v>48</v>
       </c>
       <c r="L60" s="15"/>
       <c r="M60" s="15"/>
     </row>
     <row r="61" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A61" s="15">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C61" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D61" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E61" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F61" s="2">
+        <v>9</v>
+      </c>
+      <c r="G61" s="2">
         <v>11</v>
       </c>
-      <c r="G61" s="2">
-        <v>9</v>
-      </c>
       <c r="H61" s="2">
-        <f t="shared" si="1"/>
-        <v>67</v>
+        <f>SUM(C61:G61)</f>
+        <v>65</v>
       </c>
       <c r="L61" s="15"/>
       <c r="M61" s="15"/>
     </row>
     <row r="62" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A62" s="15">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="C62" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D62" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E62" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F62" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G62" s="2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H62" s="2">
-        <f t="shared" si="1"/>
-        <v>70</v>
+        <f>SUM(C62:G62)</f>
+        <v>32</v>
       </c>
       <c r="L62" s="15"/>
       <c r="M62" s="15"/>
     </row>
     <row r="63" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A63" s="15">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="C63" s="2">
+        <v>10</v>
+      </c>
+      <c r="D63" s="2">
+        <v>4</v>
+      </c>
+      <c r="E63" s="2">
+        <v>1</v>
+      </c>
+      <c r="F63" s="2">
+        <v>2</v>
+      </c>
+      <c r="G63" s="2">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2">
+        <f>SUM(C63:G63)</f>
         <v>17</v>
-      </c>
-      <c r="D63" s="2">
-        <v>12</v>
-      </c>
-      <c r="E63" s="2">
-        <v>18</v>
-      </c>
-      <c r="F63" s="2">
-        <v>15</v>
-      </c>
-      <c r="G63" s="2">
-        <v>14</v>
-      </c>
-      <c r="H63" s="2">
-        <f t="shared" si="1"/>
-        <v>76</v>
       </c>
       <c r="L63" s="15"/>
       <c r="M63" s="15"/>
     </row>
     <row r="64" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A64" s="15">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D64" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E64" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F64" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G64" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H64" s="2">
-        <f t="shared" si="1"/>
-        <v>76</v>
+        <f>SUM(C64:G64)</f>
+        <v>47</v>
       </c>
       <c r="L64" s="15"/>
       <c r="M64" s="15"/>
     </row>
     <row r="65" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A65" s="15">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C65" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D65" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F65" s="2">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G65" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H65" s="2">
-        <f t="shared" si="1"/>
-        <v>78</v>
+        <f>SUM(C65:G65)</f>
+        <v>38</v>
       </c>
       <c r="L65" s="15"/>
       <c r="M65" s="15"/>
     </row>
     <row r="66" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A66" s="15">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="C66" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D66" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E66" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F66" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G66" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H66" s="2">
-        <f t="shared" si="1"/>
-        <v>87</v>
+        <f>SUM(C66:G66)</f>
+        <v>66</v>
       </c>
       <c r="L66" s="15"/>
       <c r="M66" s="15"/>
@@ -5558,11 +5574,6 @@
       <c r="M68" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:H3">
-    <sortState ref="B4:H66">
-      <sortCondition ref="H3"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/MONTHLY TEST.xlsx
+++ b/MONTHLY TEST.xlsx
@@ -20,7 +20,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$A$3:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1 (2)'!$B$3:$G$66</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="234">
   <si>
     <t xml:space="preserve">12th B STUDENT DATA </t>
   </si>
@@ -732,13 +732,16 @@
   </si>
   <si>
     <t>ROLL NO</t>
+  </si>
+  <si>
+    <t>STUDENT NAME</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -768,13 +771,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
@@ -879,7 +875,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -909,23 +905,14 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="13" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -2041,7 +2028,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="2">
-        <f t="shared" ref="G36:G67" si="1">SUM(B36:F36)</f>
+        <f t="shared" ref="G36:G66" si="1">SUM(B36:F36)</f>
         <v>39</v>
       </c>
     </row>
@@ -3693,414 +3680,432 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="29.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="8.7265625" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" customWidth="1"/>
+    <col min="3" max="8" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C2" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="20">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
         <v>1</v>
       </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <f t="shared" ref="H2:H33" si="0">SUM(C2:G2)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
       <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="2">
+      <c r="H4" s="2">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="13">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2">
         <v>8</v>
       </c>
-      <c r="D4" s="2">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="E5" s="2">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="13">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <f>SUM(C4:G4)</f>
-        <v>19</v>
-      </c>
-      <c r="L4" s="13"/>
-    </row>
-    <row r="5" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="15">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <f>SUM(C5:G5)</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-    </row>
-    <row r="6" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="15">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2">
-        <v>7</v>
-      </c>
       <c r="E6" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
         <v>2</v>
       </c>
       <c r="H6" s="2">
-        <f>SUM(C6:G6)</f>
-        <v>39</v>
-      </c>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-    </row>
-    <row r="7" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="15">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="13">
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="2">
+      <c r="E7" s="2">
+        <v>15</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>6</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="13">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2">
+        <v>12</v>
+      </c>
+      <c r="E8" s="2">
+        <v>18</v>
+      </c>
+      <c r="F8" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" s="2">
         <v>14</v>
       </c>
-      <c r="D7" s="2">
+      <c r="H8" s="2">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="E7" s="2">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2">
-        <v>5</v>
-      </c>
-      <c r="H7" s="2">
-        <f>SUM(C7:G7)</f>
-        <v>42</v>
-      </c>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="15">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2">
-        <v>13</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>2</v>
-      </c>
-      <c r="H8" s="2">
-        <f>SUM(C8:G8)</f>
-        <v>18</v>
-      </c>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="15">
-        <v>6</v>
-      </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2">
         <v>17</v>
       </c>
       <c r="D9" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G9" s="2">
-        <v>6</v>
-      </c>
-      <c r="H9" s="2">
-        <f>SUM(C9:G9)</f>
-        <v>44</v>
-      </c>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="15">
         <v>7</v>
       </c>
+      <c r="H9" s="14">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="13">
+        <v>9</v>
+      </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2">
         <v>17</v>
       </c>
       <c r="D10" s="2">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2">
+        <v>19</v>
+      </c>
+      <c r="F10" s="2">
+        <v>18</v>
+      </c>
+      <c r="G10" s="2">
+        <v>15</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="13">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>15</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="13">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="2">
+      <c r="C12" s="2">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="15">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="15">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2">
         <v>18</v>
       </c>
-      <c r="F10" s="2">
+      <c r="D14" s="2">
+        <v>6</v>
+      </c>
+      <c r="E14" s="2">
         <v>15</v>
       </c>
-      <c r="G10" s="2">
+      <c r="F14" s="2">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="13">
         <v>14</v>
       </c>
-      <c r="H10" s="2">
-        <f>SUM(C10:G10)</f>
-        <v>76</v>
-      </c>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="15">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2">
-        <v>17</v>
-      </c>
-      <c r="D11" s="2">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="13">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2">
         <v>16</v>
-      </c>
-      <c r="F11" s="2">
-        <v>9</v>
-      </c>
-      <c r="G11" s="2">
-        <v>7</v>
-      </c>
-      <c r="H11" s="17">
-        <f>SUM(C11:G11)</f>
-        <v>61</v>
-      </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-    </row>
-    <row r="12" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="15">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="2">
-        <v>17</v>
-      </c>
-      <c r="D12" s="2">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2">
-        <v>19</v>
-      </c>
-      <c r="F12" s="2">
-        <v>18</v>
-      </c>
-      <c r="G12" s="2">
-        <v>15</v>
-      </c>
-      <c r="H12" s="2">
-        <f>SUM(C12:G12)</f>
-        <v>87</v>
-      </c>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-    </row>
-    <row r="13" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="15">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="2">
-        <v>14</v>
-      </c>
-      <c r="D13" s="2">
-        <v>5</v>
-      </c>
-      <c r="E13" s="2">
-        <v>15</v>
-      </c>
-      <c r="F13" s="2">
-        <v>5</v>
-      </c>
-      <c r="G13" s="2">
-        <v>5</v>
-      </c>
-      <c r="H13" s="2">
-        <f>SUM(C13:G13)</f>
-        <v>44</v>
-      </c>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-    </row>
-    <row r="14" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="15">
-        <v>11</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2">
-        <v>11</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>9</v>
-      </c>
-      <c r="F14" s="2">
-        <v>2</v>
-      </c>
-      <c r="G14" s="2">
-        <v>3</v>
-      </c>
-      <c r="H14" s="2">
-        <f>SUM(C14:G14)</f>
-        <v>25</v>
-      </c>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-    </row>
-    <row r="15" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="18">
-        <v>12</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="2">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>11</v>
-      </c>
-      <c r="F15" s="2">
-        <v>10</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <f>SUM(C15:G15)</f>
-        <v>30</v>
-      </c>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-    </row>
-    <row r="16" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="18">
-        <v>13</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2">
-        <v>18</v>
-      </c>
-      <c r="D16" s="2">
-        <v>6</v>
-      </c>
-      <c r="E16" s="2">
-        <v>15</v>
       </c>
       <c r="F16" s="2">
         <v>6</v>
@@ -4109,288 +4114,268 @@
         <v>12</v>
       </c>
       <c r="H16" s="2">
-        <f>SUM(C16:G16)</f>
-        <v>57</v>
-      </c>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="15">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="13">
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H17" s="2">
-        <f>SUM(C17:G17)</f>
-        <v>15</v>
-      </c>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-    </row>
-    <row r="18" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="15">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="13">
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2">
         <v>13</v>
       </c>
       <c r="D18" s="2">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>4</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="13">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2">
         <v>11</v>
       </c>
-      <c r="E18" s="2">
+      <c r="D19" s="2">
+        <v>6</v>
+      </c>
+      <c r="E19" s="2">
+        <v>13</v>
+      </c>
+      <c r="F19" s="2">
+        <v>5</v>
+      </c>
+      <c r="G19" s="2">
+        <v>2</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="13">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2">
+        <v>7</v>
+      </c>
+      <c r="G20" s="2">
+        <v>3</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="13">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2">
         <v>16</v>
       </c>
-      <c r="F18" s="2">
-        <v>6</v>
-      </c>
-      <c r="G18" s="2">
-        <v>12</v>
-      </c>
-      <c r="H18" s="2">
-        <f>SUM(C18:G18)</f>
-        <v>58</v>
-      </c>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="15">
-        <v>16</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="2">
-        <v>15</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="D21" s="2">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>9</v>
+      </c>
+      <c r="F21" s="2">
         <v>4</v>
-      </c>
-      <c r="E19" s="2">
-        <v>17</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2">
-        <v>8</v>
-      </c>
-      <c r="H19" s="2">
-        <f>SUM(C19:G19)</f>
-        <v>45</v>
-      </c>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="15">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="2">
-        <v>13</v>
-      </c>
-      <c r="D20" s="2">
-        <v>4</v>
-      </c>
-      <c r="E20" s="2">
-        <v>15</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2">
-        <v>4</v>
-      </c>
-      <c r="H20" s="2">
-        <f>SUM(C20:G20)</f>
-        <v>36</v>
-      </c>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-    </row>
-    <row r="21" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="15">
-        <v>18</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="2">
-        <v>11</v>
-      </c>
-      <c r="D21" s="2">
-        <v>6</v>
-      </c>
-      <c r="E21" s="2">
-        <v>13</v>
-      </c>
-      <c r="F21" s="2">
-        <v>5</v>
       </c>
       <c r="G21" s="2">
         <v>2</v>
       </c>
       <c r="H21" s="2">
-        <f>SUM(C21:G21)</f>
-        <v>37</v>
-      </c>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-    </row>
-    <row r="22" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="15">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="13">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2">
+        <v>5</v>
+      </c>
+      <c r="E22" s="2">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="13">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2">
+        <v>14</v>
+      </c>
+      <c r="D23" s="2">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2">
         <v>19</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="2">
-        <v>14</v>
-      </c>
-      <c r="D22" s="2">
-        <v>9</v>
-      </c>
-      <c r="E22" s="2">
-        <v>10</v>
-      </c>
-      <c r="F22" s="2">
+      <c r="F23" s="2">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="13">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="13">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="2">
+        <v>16</v>
+      </c>
+      <c r="D25" s="2">
+        <v>12</v>
+      </c>
+      <c r="E25" s="2">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2">
+        <v>17</v>
+      </c>
+      <c r="G25" s="2">
+        <v>13</v>
+      </c>
+      <c r="H25" s="2">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="13">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="2">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2">
         <v>7</v>
-      </c>
-      <c r="G22" s="2">
-        <v>3</v>
-      </c>
-      <c r="H22" s="2">
-        <f>SUM(C22:G22)</f>
-        <v>43</v>
-      </c>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-    </row>
-    <row r="23" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="15">
-        <v>20</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="2">
-        <v>16</v>
-      </c>
-      <c r="D23" s="2">
-        <v>3</v>
-      </c>
-      <c r="E23" s="2">
-        <v>9</v>
-      </c>
-      <c r="F23" s="2">
-        <v>4</v>
-      </c>
-      <c r="G23" s="2">
-        <v>2</v>
-      </c>
-      <c r="H23" s="2">
-        <f>SUM(C23:G23)</f>
-        <v>34</v>
-      </c>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-    </row>
-    <row r="24" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="15">
-        <v>21</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="2">
-        <v>13</v>
-      </c>
-      <c r="D24" s="2">
-        <v>5</v>
-      </c>
-      <c r="E24" s="2">
-        <v>12</v>
-      </c>
-      <c r="F24" s="2">
-        <v>4</v>
-      </c>
-      <c r="G24" s="2">
-        <v>4</v>
-      </c>
-      <c r="H24" s="2">
-        <f>SUM(C24:G24)</f>
-        <v>38</v>
-      </c>
-      <c r="L24" s="16"/>
-      <c r="M24" s="15"/>
-    </row>
-    <row r="25" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="15">
-        <v>22</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="2">
-        <v>14</v>
-      </c>
-      <c r="D25" s="2">
-        <v>9</v>
-      </c>
-      <c r="E25" s="2">
-        <v>19</v>
-      </c>
-      <c r="F25" s="2">
-        <v>13</v>
-      </c>
-      <c r="G25" s="2">
-        <v>15</v>
-      </c>
-      <c r="H25" s="2">
-        <f>SUM(C25:G25)</f>
-        <v>70</v>
-      </c>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-    </row>
-    <row r="26" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="15">
-        <v>23</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="2">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <v>2</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
@@ -4399,517 +4384,481 @@
         <v>1</v>
       </c>
       <c r="H26" s="2">
-        <f>SUM(C26:G26)</f>
-        <v>3</v>
-      </c>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-    </row>
-    <row r="27" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="15">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="13">
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C27" s="2">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2">
+        <v>10</v>
+      </c>
+      <c r="E27" s="2">
+        <v>19</v>
+      </c>
+      <c r="F27" s="2">
+        <v>13</v>
+      </c>
+      <c r="G27" s="2">
+        <v>7</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="13">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="2">
         <v>16</v>
-      </c>
-      <c r="D27" s="2">
-        <v>12</v>
-      </c>
-      <c r="E27" s="2">
-        <v>20</v>
-      </c>
-      <c r="F27" s="2">
-        <v>17</v>
-      </c>
-      <c r="G27" s="2">
-        <v>13</v>
-      </c>
-      <c r="H27" s="2">
-        <f>SUM(C27:G27)</f>
-        <v>78</v>
-      </c>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-    </row>
-    <row r="28" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="15">
-        <v>25</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="2">
-        <v>8</v>
       </c>
       <c r="D28" s="2">
         <v>5</v>
       </c>
       <c r="E28" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G28" s="2">
+        <v>8</v>
+      </c>
+      <c r="H28" s="2">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="13">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="2">
+        <v>14</v>
+      </c>
+      <c r="D29" s="2">
+        <v>9</v>
+      </c>
+      <c r="E29" s="2">
+        <v>18</v>
+      </c>
+      <c r="F29" s="2">
+        <v>9</v>
+      </c>
+      <c r="G29" s="2">
+        <v>14</v>
+      </c>
+      <c r="H29" s="2">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="13">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2">
+        <v>14</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3</v>
+      </c>
+      <c r="E30" s="2">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="13">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="2">
+        <v>13</v>
+      </c>
+      <c r="D31" s="2">
+        <v>5</v>
+      </c>
+      <c r="E31" s="2">
+        <v>12</v>
+      </c>
+      <c r="F31" s="2">
+        <v>6</v>
+      </c>
+      <c r="G31" s="2">
+        <v>4</v>
+      </c>
+      <c r="H31" s="2">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="13">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="2">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2">
         <v>1</v>
       </c>
-      <c r="H28" s="2">
-        <f>SUM(C28:G28)</f>
-        <v>21</v>
-      </c>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-    </row>
-    <row r="29" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="15">
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="13">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="2">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>6</v>
+      </c>
+      <c r="F33" s="2">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="13">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="2">
+        <v>15</v>
+      </c>
+      <c r="D34" s="2">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2">
+        <v>14</v>
+      </c>
+      <c r="F34" s="2">
+        <v>16</v>
+      </c>
+      <c r="G34" s="2">
+        <v>6</v>
+      </c>
+      <c r="H34" s="2">
+        <f t="shared" ref="H34:H65" si="1">SUM(C34:G34)</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="13">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="2">
+        <v>16</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2">
+        <v>10</v>
+      </c>
+      <c r="F35" s="2">
+        <v>3</v>
+      </c>
+      <c r="G35" s="2">
+        <v>3</v>
+      </c>
+      <c r="H35" s="2">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="13">
+        <v>36</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="2">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>10</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2">
+        <v>2</v>
+      </c>
+      <c r="H36" s="2">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="13">
+        <v>37</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="2">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2">
+        <v>4</v>
+      </c>
+      <c r="E37" s="2">
+        <v>16</v>
+      </c>
+      <c r="F37" s="2">
+        <v>2</v>
+      </c>
+      <c r="G37" s="2">
+        <v>2</v>
+      </c>
+      <c r="H37" s="2">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="13">
+        <v>38</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="2">
+        <v>15</v>
+      </c>
+      <c r="D38" s="2">
+        <v>14</v>
+      </c>
+      <c r="E38" s="2">
+        <v>18</v>
+      </c>
+      <c r="F38" s="2">
+        <v>17</v>
+      </c>
+      <c r="G38" s="2">
+        <v>12</v>
+      </c>
+      <c r="H38" s="2">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="13">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="2">
+        <v>11</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2">
+        <v>6</v>
+      </c>
+      <c r="F39" s="2">
+        <v>8</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2">
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="2">
-        <v>12</v>
-      </c>
-      <c r="D29" s="2">
+    </row>
+    <row r="40" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="13">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="2">
+        <v>18</v>
+      </c>
+      <c r="D40" s="2">
         <v>10</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E40" s="2">
         <v>19</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F40" s="2">
+        <v>11</v>
+      </c>
+      <c r="G40" s="2">
+        <v>9</v>
+      </c>
+      <c r="H40" s="2">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="13">
+        <v>41</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="2">
         <v>13</v>
       </c>
-      <c r="G29" s="2">
-        <v>7</v>
-      </c>
-      <c r="H29" s="2">
-        <f>SUM(C29:G29)</f>
-        <v>61</v>
-      </c>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-    </row>
-    <row r="30" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="15">
-        <v>27</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="2">
-        <v>16</v>
-      </c>
-      <c r="D30" s="2">
-        <v>5</v>
-      </c>
-      <c r="E30" s="2">
-        <v>12</v>
-      </c>
-      <c r="F30" s="2">
-        <v>8</v>
-      </c>
-      <c r="G30" s="2">
-        <v>8</v>
-      </c>
-      <c r="H30" s="2">
-        <f>SUM(C30:G30)</f>
-        <v>49</v>
-      </c>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-    </row>
-    <row r="31" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="15">
-        <v>28</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="2">
-        <v>14</v>
-      </c>
-      <c r="D31" s="2">
-        <v>9</v>
-      </c>
-      <c r="E31" s="2">
-        <v>18</v>
-      </c>
-      <c r="F31" s="2">
-        <v>9</v>
-      </c>
-      <c r="G31" s="2">
-        <v>14</v>
-      </c>
-      <c r="H31" s="2">
-        <f>SUM(C31:G31)</f>
-        <v>64</v>
-      </c>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-    </row>
-    <row r="32" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="15">
-        <v>29</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="2">
-        <v>14</v>
-      </c>
-      <c r="D32" s="2">
-        <v>3</v>
-      </c>
-      <c r="E32" s="2">
-        <v>11</v>
-      </c>
-      <c r="F32" s="2">
-        <v>5</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2">
-        <f>SUM(C32:G32)</f>
-        <v>33</v>
-      </c>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-    </row>
-    <row r="33" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="15">
-        <v>30</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="2">
-        <v>13</v>
-      </c>
-      <c r="D33" s="2">
-        <v>5</v>
-      </c>
-      <c r="E33" s="2">
-        <v>12</v>
-      </c>
-      <c r="F33" s="2">
-        <v>6</v>
-      </c>
-      <c r="G33" s="2">
-        <v>4</v>
-      </c>
-      <c r="H33" s="2">
-        <f>SUM(C33:G33)</f>
-        <v>40</v>
-      </c>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-    </row>
-    <row r="34" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="15">
-        <v>31</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="2">
-        <v>5</v>
-      </c>
-      <c r="D34" s="2">
-        <v>1</v>
-      </c>
-      <c r="E34" s="2">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2">
-        <f>SUM(C34:G34)</f>
-        <v>6</v>
-      </c>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-    </row>
-    <row r="35" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="15">
-        <v>32</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="2">
-        <v>15</v>
-      </c>
-      <c r="D35" s="2">
-        <v>0</v>
-      </c>
-      <c r="E35" s="2">
-        <v>6</v>
-      </c>
-      <c r="F35" s="2">
+      <c r="D41" s="2">
         <v>2</v>
       </c>
-      <c r="G35" s="2">
-        <v>1</v>
-      </c>
-      <c r="H35" s="2">
-        <f>SUM(C35:G35)</f>
-        <v>24</v>
-      </c>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-    </row>
-    <row r="36" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="15">
-        <v>33</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="2">
-        <v>15</v>
-      </c>
-      <c r="D36" s="2">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2">
-        <v>14</v>
-      </c>
-      <c r="F36" s="2">
-        <v>16</v>
-      </c>
-      <c r="G36" s="2">
-        <v>6</v>
-      </c>
-      <c r="H36" s="2">
-        <f>SUM(C36:G36)</f>
-        <v>59</v>
-      </c>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-    </row>
-    <row r="37" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="15">
-        <v>35</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="2">
-        <v>16</v>
-      </c>
-      <c r="D37" s="2">
-        <v>1</v>
-      </c>
-      <c r="E37" s="2">
-        <v>10</v>
-      </c>
-      <c r="F37" s="2">
-        <v>3</v>
-      </c>
-      <c r="G37" s="2">
-        <v>3</v>
-      </c>
-      <c r="H37" s="2">
-        <f>SUM(C37:G37)</f>
-        <v>33</v>
-      </c>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-    </row>
-    <row r="38" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="15">
-        <v>36</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="2">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2">
-        <v>2</v>
-      </c>
-      <c r="E38" s="2">
-        <v>10</v>
-      </c>
-      <c r="F38" s="2">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2">
-        <v>2</v>
-      </c>
-      <c r="H38" s="2">
-        <f>SUM(C38:G38)</f>
-        <v>24</v>
-      </c>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-    </row>
-    <row r="39" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="15">
-        <v>37</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="2">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2">
-        <v>4</v>
-      </c>
-      <c r="E39" s="2">
-        <v>16</v>
-      </c>
-      <c r="F39" s="2">
-        <v>2</v>
-      </c>
-      <c r="G39" s="2">
-        <v>2</v>
-      </c>
-      <c r="H39" s="2">
-        <f>SUM(C39:G39)</f>
-        <v>32</v>
-      </c>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-    </row>
-    <row r="40" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="15">
-        <v>38</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="2">
-        <v>15</v>
-      </c>
-      <c r="D40" s="2">
-        <v>14</v>
-      </c>
-      <c r="E40" s="2">
-        <v>18</v>
-      </c>
-      <c r="F40" s="2">
+      <c r="E41" s="2">
         <v>17</v>
-      </c>
-      <c r="G40" s="2">
-        <v>12</v>
-      </c>
-      <c r="H40" s="2">
-        <f>SUM(C40:G40)</f>
-        <v>76</v>
-      </c>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-    </row>
-    <row r="41" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="15">
-        <v>39</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="2">
-        <v>11</v>
-      </c>
-      <c r="D41" s="2">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2">
-        <v>6</v>
       </c>
       <c r="F41" s="2">
         <v>8</v>
       </c>
       <c r="G41" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H41" s="2">
-        <f>SUM(C41:G41)</f>
-        <v>26</v>
-      </c>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-    </row>
-    <row r="42" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="15">
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="13">
+        <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C42" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D42" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E42" s="2">
+        <v>3</v>
+      </c>
+      <c r="F42" s="2">
+        <v>7</v>
+      </c>
+      <c r="G42" s="2">
+        <v>3</v>
+      </c>
+      <c r="H42" s="2">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="13">
+        <v>43</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="2">
         <v>19</v>
       </c>
-      <c r="F42" s="2">
-        <v>11</v>
-      </c>
-      <c r="G42" s="2">
-        <v>9</v>
-      </c>
-      <c r="H42" s="2">
-        <f>SUM(C42:G42)</f>
-        <v>67</v>
-      </c>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-    </row>
-    <row r="43" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="15">
-        <v>41</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="2">
+      <c r="D43" s="2">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2">
         <v>13</v>
-      </c>
-      <c r="D43" s="2">
-        <v>2</v>
-      </c>
-      <c r="E43" s="2">
-        <v>17</v>
       </c>
       <c r="F43" s="2">
         <v>8</v>
       </c>
       <c r="G43" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H43" s="2">
-        <f>SUM(C43:G43)</f>
-        <v>47</v>
-      </c>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
-    </row>
-    <row r="44" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="15">
-        <v>42</v>
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="13">
+        <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C44" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E44" s="2">
         <v>3</v>
@@ -4921,657 +4870,549 @@
         <v>3</v>
       </c>
       <c r="H44" s="2">
-        <f>SUM(C44:G44)</f>
-        <v>37</v>
-      </c>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
-    </row>
-    <row r="45" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="15">
-        <v>43</v>
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="13">
+        <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C45" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D45" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E45" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F45" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G45" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H45" s="2">
-        <f>SUM(C45:G45)</f>
-        <v>52</v>
-      </c>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-    </row>
-    <row r="46" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="15">
-        <v>44</v>
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="13">
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C46" s="2">
+        <v>15</v>
+      </c>
+      <c r="D46" s="2">
+        <v>6</v>
+      </c>
+      <c r="E46" s="2">
+        <v>10</v>
+      </c>
+      <c r="F46" s="2">
         <v>9</v>
       </c>
-      <c r="D46" s="2">
-        <v>4</v>
-      </c>
-      <c r="E46" s="2">
-        <v>3</v>
-      </c>
-      <c r="F46" s="2">
-        <v>7</v>
-      </c>
       <c r="G46" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H46" s="2">
-        <f>SUM(C46:G46)</f>
-        <v>26</v>
-      </c>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-    </row>
-    <row r="47" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="15">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="13">
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C47" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D47" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E47" s="2">
         <v>1</v>
       </c>
       <c r="F47" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H47" s="2">
-        <f>SUM(C47:G47)</f>
-        <v>26</v>
-      </c>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-    </row>
-    <row r="48" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="15">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="13">
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C48" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D48" s="2">
         <v>6</v>
       </c>
       <c r="E48" s="2">
+        <v>5</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2">
+        <v>2</v>
+      </c>
+      <c r="H48" s="2">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="13">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" s="2">
+        <v>14</v>
+      </c>
+      <c r="D49" s="2">
+        <v>3</v>
+      </c>
+      <c r="E49" s="2">
         <v>10</v>
       </c>
-      <c r="F48" s="2">
-        <v>9</v>
-      </c>
-      <c r="G48" s="2">
-        <v>11</v>
-      </c>
-      <c r="H48" s="2">
-        <f>SUM(C48:G48)</f>
-        <v>51</v>
-      </c>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-    </row>
-    <row r="49" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="15">
-        <v>46</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="2">
-        <v>5</v>
-      </c>
-      <c r="D49" s="2">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2">
+      <c r="F49" s="2">
+        <v>6</v>
+      </c>
+      <c r="G49" s="2">
         <v>1</v>
       </c>
-      <c r="F49" s="2">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2">
+      <c r="H49" s="2">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="13">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" s="2">
+        <v>12</v>
+      </c>
+      <c r="D50" s="2">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2</v>
+      </c>
+      <c r="F50" s="2">
         <v>6</v>
-      </c>
-      <c r="H49" s="2">
-        <f>SUM(C49:G49)</f>
-        <v>12</v>
-      </c>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-    </row>
-    <row r="50" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="15">
-        <v>47</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C50" s="2">
-        <v>14</v>
-      </c>
-      <c r="D50" s="2">
-        <v>6</v>
-      </c>
-      <c r="E50" s="2">
-        <v>5</v>
-      </c>
-      <c r="F50" s="2">
-        <v>1</v>
       </c>
       <c r="G50" s="2">
         <v>2</v>
       </c>
       <c r="H50" s="2">
-        <f>SUM(C50:G50)</f>
-        <v>28</v>
-      </c>
-      <c r="L50" s="15"/>
-      <c r="M50" s="15"/>
-    </row>
-    <row r="51" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="15">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="13">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" s="2">
+        <v>16</v>
+      </c>
+      <c r="D51" s="2">
+        <v>5</v>
+      </c>
+      <c r="E51" s="2">
+        <v>9</v>
+      </c>
+      <c r="F51" s="2">
+        <v>5</v>
+      </c>
+      <c r="G51" s="2">
+        <v>12</v>
+      </c>
+      <c r="H51" s="2">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="13">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="2">
+        <v>16</v>
+      </c>
+      <c r="D52" s="2">
+        <v>7</v>
+      </c>
+      <c r="E52" s="2">
+        <v>16</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2">
+        <v>7</v>
+      </c>
+      <c r="H52" s="2">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="13">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="2">
+        <v>6</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2">
+        <v>2</v>
+      </c>
+      <c r="G53" s="2">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="13">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="2">
+        <v>11</v>
+      </c>
+      <c r="D54" s="2">
+        <v>0</v>
+      </c>
+      <c r="E54" s="2">
+        <v>15</v>
+      </c>
+      <c r="F54" s="2">
+        <v>13</v>
+      </c>
+      <c r="G54" s="2">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="13">
+        <v>54</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="2">
+        <v>4</v>
+      </c>
+      <c r="D55" s="2">
+        <v>4</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="13">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="2">
+        <v>12</v>
+      </c>
+      <c r="D56" s="2">
+        <v>9</v>
+      </c>
+      <c r="E56" s="2">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2">
+        <v>7</v>
+      </c>
+      <c r="G56" s="2">
+        <v>13</v>
+      </c>
+      <c r="H56" s="2">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="13">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="2">
+        <v>18</v>
+      </c>
+      <c r="D57" s="2">
+        <v>6</v>
+      </c>
+      <c r="E57" s="2">
+        <v>6</v>
+      </c>
+      <c r="F57" s="2">
+        <v>4</v>
+      </c>
+      <c r="G57" s="2">
+        <v>4</v>
+      </c>
+      <c r="H57" s="2">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="13">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="2">
+        <v>18</v>
+      </c>
+      <c r="D58" s="2">
+        <v>11</v>
+      </c>
+      <c r="E58" s="2">
+        <v>9</v>
+      </c>
+      <c r="F58" s="2">
+        <v>4</v>
+      </c>
+      <c r="G58" s="2">
+        <v>6</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C51" s="2">
+    </row>
+    <row r="59" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="13">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="2">
+        <v>19</v>
+      </c>
+      <c r="D59" s="2">
+        <v>11</v>
+      </c>
+      <c r="E59" s="2">
+        <v>15</v>
+      </c>
+      <c r="F59" s="2">
+        <v>9</v>
+      </c>
+      <c r="G59" s="2">
+        <v>11</v>
+      </c>
+      <c r="H59" s="2">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="13">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="2">
+        <v>12</v>
+      </c>
+      <c r="D60" s="2">
+        <v>8</v>
+      </c>
+      <c r="E60" s="2">
+        <v>7</v>
+      </c>
+      <c r="F60" s="2">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2">
+        <v>4</v>
+      </c>
+      <c r="H60" s="2">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="13">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C61" s="2">
+        <v>10</v>
+      </c>
+      <c r="D61" s="2">
+        <v>4</v>
+      </c>
+      <c r="E61" s="2">
+        <v>1</v>
+      </c>
+      <c r="F61" s="2">
+        <v>2</v>
+      </c>
+      <c r="G61" s="2">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="13">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" s="2">
+        <v>13</v>
+      </c>
+      <c r="D62" s="2">
+        <v>5</v>
+      </c>
+      <c r="E62" s="2">
+        <v>12</v>
+      </c>
+      <c r="F62" s="2">
+        <v>7</v>
+      </c>
+      <c r="G62" s="2">
+        <v>10</v>
+      </c>
+      <c r="H62" s="2">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="13">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="2">
         <v>14</v>
       </c>
-      <c r="D51" s="2">
-        <v>3</v>
-      </c>
-      <c r="E51" s="2">
-        <v>10</v>
-      </c>
-      <c r="F51" s="2">
+      <c r="D63" s="2">
         <v>6</v>
       </c>
-      <c r="G51" s="2">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2">
-        <f>SUM(C51:G51)</f>
-        <v>34</v>
-      </c>
-      <c r="L51" s="15"/>
-      <c r="M51" s="15"/>
-    </row>
-    <row r="52" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="15">
-        <v>49</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="2">
-        <v>12</v>
-      </c>
-      <c r="D52" s="2">
-        <v>8</v>
-      </c>
-      <c r="E52" s="2">
-        <v>2</v>
-      </c>
-      <c r="F52" s="2">
-        <v>6</v>
-      </c>
-      <c r="G52" s="2">
-        <v>2</v>
-      </c>
-      <c r="H52" s="2">
-        <f>SUM(C52:G52)</f>
-        <v>30</v>
-      </c>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
-    </row>
-    <row r="53" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="15">
-        <v>50</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C53" s="2">
-        <v>16</v>
-      </c>
-      <c r="D53" s="2">
-        <v>5</v>
-      </c>
-      <c r="E53" s="2">
+      <c r="E63" s="2">
         <v>9</v>
-      </c>
-      <c r="F53" s="2">
-        <v>5</v>
-      </c>
-      <c r="G53" s="2">
-        <v>12</v>
-      </c>
-      <c r="H53" s="2">
-        <f>SUM(C53:G53)</f>
-        <v>47</v>
-      </c>
-      <c r="L53" s="15"/>
-      <c r="M53" s="15"/>
-    </row>
-    <row r="54" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="15">
-        <v>51</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C54" s="2">
-        <v>16</v>
-      </c>
-      <c r="D54" s="2">
-        <v>7</v>
-      </c>
-      <c r="E54" s="2">
-        <v>16</v>
-      </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2">
-        <v>7</v>
-      </c>
-      <c r="H54" s="2">
-        <f>SUM(C54:G54)</f>
-        <v>46</v>
-      </c>
-      <c r="L54" s="15"/>
-      <c r="M54" s="15"/>
-    </row>
-    <row r="55" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="15">
-        <v>52</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" s="2">
-        <v>6</v>
-      </c>
-      <c r="D55" s="2">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2">
-        <v>0</v>
-      </c>
-      <c r="F55" s="2">
-        <v>2</v>
-      </c>
-      <c r="G55" s="2">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2">
-        <f>SUM(C55:G55)</f>
-        <v>8</v>
-      </c>
-      <c r="L55" s="16"/>
-      <c r="M55" s="15"/>
-    </row>
-    <row r="56" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="15">
-        <v>53</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C56" s="2">
-        <v>11</v>
-      </c>
-      <c r="D56" s="2">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2">
-        <v>15</v>
-      </c>
-      <c r="F56" s="2">
-        <v>13</v>
-      </c>
-      <c r="G56" s="2">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2">
-        <f>SUM(C56:G56)</f>
-        <v>39</v>
-      </c>
-      <c r="L56" s="15"/>
-      <c r="M56" s="15"/>
-    </row>
-    <row r="57" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="15">
-        <v>54</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" s="2">
-        <v>4</v>
-      </c>
-      <c r="D57" s="2">
-        <v>4</v>
-      </c>
-      <c r="E57" s="2">
-        <v>0</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0</v>
-      </c>
-      <c r="G57" s="2">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2">
-        <f>SUM(C57:G57)</f>
-        <v>8</v>
-      </c>
-      <c r="L57" s="15"/>
-      <c r="M57" s="15"/>
-    </row>
-    <row r="58" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="15">
-        <v>55</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C58" s="2">
-        <v>12</v>
-      </c>
-      <c r="D58" s="2">
-        <v>9</v>
-      </c>
-      <c r="E58" s="2">
-        <v>11</v>
-      </c>
-      <c r="F58" s="2">
-        <v>7</v>
-      </c>
-      <c r="G58" s="2">
-        <v>13</v>
-      </c>
-      <c r="H58" s="2">
-        <f>SUM(C58:G58)</f>
-        <v>52</v>
-      </c>
-      <c r="L58" s="15"/>
-      <c r="M58" s="15"/>
-    </row>
-    <row r="59" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="15">
-        <v>56</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C59" s="2">
-        <v>18</v>
-      </c>
-      <c r="D59" s="2">
-        <v>6</v>
-      </c>
-      <c r="E59" s="2">
-        <v>6</v>
-      </c>
-      <c r="F59" s="2">
-        <v>4</v>
-      </c>
-      <c r="G59" s="2">
-        <v>4</v>
-      </c>
-      <c r="H59" s="2">
-        <f>SUM(C59:G59)</f>
-        <v>38</v>
-      </c>
-      <c r="L59" s="15"/>
-      <c r="M59" s="15"/>
-    </row>
-    <row r="60" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="15">
-        <v>57</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" s="2">
-        <v>18</v>
-      </c>
-      <c r="D60" s="2">
-        <v>11</v>
-      </c>
-      <c r="E60" s="2">
-        <v>9</v>
-      </c>
-      <c r="F60" s="2">
-        <v>4</v>
-      </c>
-      <c r="G60" s="2">
-        <v>6</v>
-      </c>
-      <c r="H60" s="2">
-        <f>SUM(C60:G60)</f>
-        <v>48</v>
-      </c>
-      <c r="L60" s="15"/>
-      <c r="M60" s="15"/>
-    </row>
-    <row r="61" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="15">
-        <v>58</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C61" s="2">
-        <v>19</v>
-      </c>
-      <c r="D61" s="2">
-        <v>11</v>
-      </c>
-      <c r="E61" s="2">
-        <v>15</v>
-      </c>
-      <c r="F61" s="2">
-        <v>9</v>
-      </c>
-      <c r="G61" s="2">
-        <v>11</v>
-      </c>
-      <c r="H61" s="2">
-        <f>SUM(C61:G61)</f>
-        <v>65</v>
-      </c>
-      <c r="L61" s="15"/>
-      <c r="M61" s="15"/>
-    </row>
-    <row r="62" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="15">
-        <v>59</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C62" s="2">
-        <v>12</v>
-      </c>
-      <c r="D62" s="2">
-        <v>8</v>
-      </c>
-      <c r="E62" s="2">
-        <v>7</v>
-      </c>
-      <c r="F62" s="2">
-        <v>1</v>
-      </c>
-      <c r="G62" s="2">
-        <v>4</v>
-      </c>
-      <c r="H62" s="2">
-        <f>SUM(C62:G62)</f>
-        <v>32</v>
-      </c>
-      <c r="L62" s="15"/>
-      <c r="M62" s="15"/>
-    </row>
-    <row r="63" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="15">
-        <v>60</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C63" s="2">
-        <v>10</v>
-      </c>
-      <c r="D63" s="2">
-        <v>4</v>
-      </c>
-      <c r="E63" s="2">
-        <v>1</v>
       </c>
       <c r="F63" s="2">
         <v>2</v>
       </c>
       <c r="G63" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H63" s="2">
-        <f>SUM(C63:G63)</f>
-        <v>17</v>
-      </c>
-      <c r="L63" s="15"/>
-      <c r="M63" s="15"/>
-    </row>
-    <row r="64" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="15">
-        <v>61</v>
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="13">
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C64" s="2">
+        <v>16</v>
+      </c>
+      <c r="D64" s="2">
         <v>13</v>
       </c>
-      <c r="D64" s="2">
-        <v>5</v>
-      </c>
       <c r="E64" s="2">
+        <v>14</v>
+      </c>
+      <c r="F64" s="2">
         <v>12</v>
       </c>
-      <c r="F64" s="2">
-        <v>7</v>
-      </c>
       <c r="G64" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H64" s="2">
-        <f>SUM(C64:G64)</f>
-        <v>47</v>
-      </c>
-      <c r="L64" s="15"/>
-      <c r="M64" s="15"/>
-    </row>
-    <row r="65" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="15">
-        <v>62</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C65" s="2">
-        <v>14</v>
-      </c>
-      <c r="D65" s="2">
-        <v>6</v>
-      </c>
-      <c r="E65" s="2">
-        <v>9</v>
-      </c>
-      <c r="F65" s="2">
-        <v>2</v>
-      </c>
-      <c r="G65" s="2">
-        <v>7</v>
-      </c>
-      <c r="H65" s="2">
-        <f>SUM(C65:G65)</f>
-        <v>38</v>
-      </c>
-      <c r="L65" s="15"/>
-      <c r="M65" s="15"/>
-    </row>
-    <row r="66" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="15">
-        <v>63</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C66" s="2">
-        <v>16</v>
-      </c>
-      <c r="D66" s="2">
-        <v>13</v>
-      </c>
-      <c r="E66" s="2">
-        <v>14</v>
-      </c>
-      <c r="F66" s="2">
-        <v>12</v>
-      </c>
-      <c r="G66" s="2">
-        <v>11</v>
-      </c>
-      <c r="H66" s="2">
-        <f>SUM(C66:G66)</f>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="L66" s="15"/>
-      <c r="M66" s="15"/>
-    </row>
-    <row r="67" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="L67" s="15"/>
-      <c r="M67" s="15"/>
-    </row>
-    <row r="68" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="L68" s="15"/>
-      <c r="M68" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
